--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.4629,0.2009,0.0089,0.3180</t>
-  </si>
-  <si>
-    <t>0.0103,0.0512,0.0017,0.9925</t>
-  </si>
-  <si>
-    <t>0.1903,0.1292,0.0044,0.7301</t>
-  </si>
-  <si>
-    <t>0.0188,0.0197,0.0035,0.9880</t>
-  </si>
-  <si>
-    <t>0.9779,0.0437,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9752,0.0301,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.9832,0.0257,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9818,0.0239,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.9832,0.0269,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9659,0.0597,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9856,0.0209,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9832,0.0182,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.0265,0.9712,0.0178,0.0046</t>
-  </si>
-  <si>
-    <t>0.1846,0.4813,0.4377,0.0787</t>
-  </si>
-  <si>
-    <t>0.0486,0.9191,0.1241,0.0101</t>
-  </si>
-  <si>
-    <t>0.0577,0.7807,0.3809,0.0113</t>
-  </si>
-  <si>
-    <t>0.1743,0.7873,0.1375,0.0249</t>
-  </si>
-  <si>
-    <t>0.0022,0.9976,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.0050,0.9957,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.0363,0.9752,0.0030,0.0023</t>
-  </si>
-  <si>
-    <t>0.0034,0.9960,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.0033,0.9965,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0570,0.8710,0.1820,0.0388</t>
-  </si>
-  <si>
-    <t>0.0219,0.8896,0.0225,0.3426</t>
-  </si>
-  <si>
-    <t>0.0380,0.1532,0.8971,0.0516</t>
-  </si>
-  <si>
-    <t>0.2302,0.1871,0.5433,0.0915</t>
-  </si>
-  <si>
-    <t>0.1279,0.1577,0.7963,0.0338</t>
-  </si>
-  <si>
-    <t>0.1166,0.7125,0.3653,0.0617</t>
-  </si>
-  <si>
-    <t>0.0188,0.0884,0.9034,0.0988</t>
-  </si>
-  <si>
-    <t>0.3720,0.7541,0.0102,0.0071</t>
-  </si>
-  <si>
-    <t>0.1136,0.8862,0.0730,0.0095</t>
-  </si>
-  <si>
-    <t>0.0374,0.1300,0.8942,0.0607</t>
-  </si>
-  <si>
-    <t>0.0128,0.9842,0.0236,0.0007</t>
-  </si>
-  <si>
-    <t>0.3057,0.7755,0.0256,0.0084</t>
-  </si>
-  <si>
-    <t>0.4973,0.5738,0.0281,0.0080</t>
-  </si>
-  <si>
-    <t>0.2563,0.8325,0.0111,0.0027</t>
-  </si>
-  <si>
-    <t>0.0078,0.9906,0.0199,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.9783,0.0045,0.1586</t>
-  </si>
-  <si>
-    <t>0.0076,0.8075,0.0576,0.5990</t>
-  </si>
-  <si>
-    <t>0.0081,0.9718,0.1725,0.0071</t>
-  </si>
-  <si>
-    <t>0.0231,0.3037,0.0326,0.9085</t>
-  </si>
-  <si>
-    <t>0.0118,0.9437,0.2217,0.0145</t>
-  </si>
-  <si>
-    <t>0.0016,0.9969,0.0015,0.0020</t>
-  </si>
-  <si>
-    <t>0.0294,0.7848,0.4305,0.1057</t>
-  </si>
-  <si>
-    <t>0.0188,0.9054,0.0051,0.4654</t>
-  </si>
-  <si>
-    <t>0.0005,0.9984,0.0006,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0106,0.7807,0.1068,0.4012</t>
-  </si>
-  <si>
-    <t>0.0106,0.7542,0.8014,0.0174</t>
-  </si>
-  <si>
-    <t>0.0531,0.5221,0.1331,0.6766</t>
-  </si>
-  <si>
-    <t>0.0569,0.1025,0.8899,0.0454</t>
-  </si>
-  <si>
-    <t>0.0426,0.5576,0.4570,0.2860</t>
-  </si>
-  <si>
-    <t>0.0313,0.3789,0.6320,0.2444</t>
-  </si>
-  <si>
-    <t>0.9109,0.1619,0.0034,0.0011</t>
-  </si>
-  <si>
-    <t>0.9675,0.0388,0.0031,0.0022</t>
-  </si>
-  <si>
-    <t>0.9493,0.0859,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.0401,0.2661,0.8827,0.0361</t>
-  </si>
-  <si>
-    <t>0.9777,0.0240,0.0015,0.0021</t>
-  </si>
-  <si>
-    <t>0.9868,0.0200,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9455,0.0969,0.0025,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.9956,0.0056,0.0101</t>
-  </si>
-  <si>
-    <t>0.0189,0.8645,0.0881,0.3421</t>
-  </si>
-  <si>
-    <t>0.0140,0.7894,0.1428,0.4719</t>
-  </si>
-  <si>
-    <t>0.0041,0.9849,0.0147,0.0508</t>
-  </si>
-  <si>
-    <t>0.0358,0.5434,0.6598,0.1109</t>
-  </si>
-  <si>
-    <t>0.0012,0.9983,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.5323,0.2628,0.2380,0.0112</t>
-  </si>
-  <si>
-    <t>0.0751,0.9335,0.0300,0.0043</t>
-  </si>
-  <si>
-    <t>0.1392,0.5075,0.5590,0.0520</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0089,0.0025</t>
-  </si>
-  <si>
-    <t>0.0011,0.9961,0.0165,0.0015</t>
-  </si>
-  <si>
-    <t>0.0010,0.9967,0.0042,0.0044</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0006,0.0479</t>
-  </si>
-  <si>
-    <t>0.0151,0.0254,0.0069,0.9874</t>
-  </si>
-  <si>
-    <t>0.0015,0.0289,0.0007,0.9985</t>
-  </si>
-  <si>
-    <t>0.0024,0.0150,0.0008,0.9981</t>
-  </si>
-  <si>
-    <t>0.0068,0.0783,0.0018,0.9934</t>
-  </si>
-  <si>
-    <t>0.0089,0.0252,0.0020,0.9935</t>
-  </si>
-  <si>
-    <t>0.0081,0.0382,0.0023,0.9934</t>
-  </si>
-  <si>
-    <t>0.0013,0.9967,0.0049,0.0058</t>
-  </si>
-  <si>
-    <t>0.0046,0.9835,0.0516,0.0175</t>
-  </si>
-  <si>
-    <t>0.0024,0.9864,0.0895,0.0073</t>
-  </si>
-  <si>
-    <t>0.0107,0.9353,0.1176,0.1140</t>
-  </si>
-  <si>
-    <t>0.0012,0.9963,0.0189,0.0014</t>
-  </si>
-  <si>
-    <t>0.0021,0.9945,0.0088,0.0087</t>
-  </si>
-  <si>
-    <t>0.9803,0.0347,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9189,0.1597,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.9275,0.1626,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9708,0.0495,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9274,0.0920,0.0045,0.0037</t>
-  </si>
-  <si>
-    <t>0.9840,0.0175,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.9624,0.0511,0.0029,0.0022</t>
-  </si>
-  <si>
-    <t>0.9725,0.0460,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.9921,0.0100,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9829,0.0304,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9916,0.0073,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9913,0.0087,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9754,0.0267,0.0018,0.0023</t>
-  </si>
-  <si>
-    <t>0.9881,0.0119,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9879,0.0108,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9882,0.0133,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.0452,0.2605,0.7947,0.1042</t>
-  </si>
-  <si>
-    <t>0.0703,0.8256,0.2981,0.0270</t>
-  </si>
-  <si>
-    <t>0.1009,0.8600,0.0613,0.0686</t>
-  </si>
-  <si>
-    <t>0.0337,0.2262,0.8334,0.0796</t>
-  </si>
-  <si>
-    <t>0.0024,0.9971,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.0054,0.9953,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.0203,0.9868,0.0012,0.0018</t>
-  </si>
-  <si>
-    <t>0.0352,0.9760,0.0038,0.0018</t>
-  </si>
-  <si>
-    <t>0.0031,0.9962,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.9991,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0866,0.9467,0.0059,0.0022</t>
-  </si>
-  <si>
-    <t>0.1180,0.8786,0.0270,0.0229</t>
-  </si>
-  <si>
-    <t>0.1919,0.2223,0.6693,0.0574</t>
-  </si>
-  <si>
-    <t>0.0676,0.8285,0.0442,0.1487</t>
-  </si>
-  <si>
-    <t>0.0425,0.9454,0.0326,0.0152</t>
-  </si>
-  <si>
-    <t>0.1139,0.5521,0.0088,0.6114</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9978,0.0013,0.0029</t>
-  </si>
-  <si>
-    <t>0.0014,0.9964,0.0008,0.0065</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.0112,0.9906,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.2129,0.8887,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.1162,0.9347,0.0085,0.0019</t>
-  </si>
-  <si>
-    <t>0.9152,0.1668,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9745,0.0238,0.0020,0.0048</t>
-  </si>
-  <si>
-    <t>0.9872,0.0134,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9782,0.0192,0.0050,0.0031</t>
-  </si>
-  <si>
-    <t>0.9880,0.0144,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.8954,0.1767,0.0039,0.0018</t>
-  </si>
-  <si>
-    <t>0.9732,0.0239,0.0029,0.0047</t>
-  </si>
-  <si>
-    <t>0.9821,0.0152,0.0050,0.0026</t>
-  </si>
-  <si>
-    <t>0.0051,0.9795,0.1097,0.0090</t>
-  </si>
-  <si>
-    <t>0.0056,0.9779,0.0509,0.0380</t>
-  </si>
-  <si>
-    <t>0.0195,0.9430,0.1028,0.0734</t>
-  </si>
-  <si>
-    <t>0.0053,0.9836,0.0576,0.0091</t>
-  </si>
-  <si>
-    <t>0.1387,0.8479,0.0183,0.0861</t>
-  </si>
-  <si>
-    <t>0.2435,0.6438,0.1239,0.0897</t>
-  </si>
-  <si>
-    <t>0.4005,0.1402,0.5221,0.0277</t>
-  </si>
-  <si>
-    <t>0.0254,0.9618,0.0217,0.0115</t>
-  </si>
-  <si>
-    <t>0.0775,0.0199,0.0015,0.9682</t>
-  </si>
-  <si>
-    <t>0.0007,0.0040,0.0008,0.9992</t>
-  </si>
-  <si>
-    <t>0.0011,0.1212,0.0013,0.9976</t>
-  </si>
-  <si>
-    <t>0.0101,0.0146,0.0012,0.9937</t>
-  </si>
-  <si>
-    <t>0.0020,0.9885,0.0188,0.0353</t>
-  </si>
-  <si>
-    <t>0.9460,0.0736,0.0014,0.0038</t>
-  </si>
-  <si>
-    <t>0.0243,0.9814,0.0019,0.0048</t>
-  </si>
-  <si>
-    <t>0.9869,0.0084,0.0023,0.0030</t>
-  </si>
-  <si>
-    <t>0.3600,0.8099,0.0022,0.0031</t>
-  </si>
-  <si>
-    <t>0.9585,0.0289,0.0032,0.0104</t>
-  </si>
-  <si>
-    <t>0.1788,0.0288,0.0173,0.8784</t>
-  </si>
-  <si>
-    <t>0.8991,0.1032,0.0163,0.0079</t>
-  </si>
-  <si>
-    <t>0.0292,0.4990,0.7649,0.0706</t>
-  </si>
-  <si>
-    <t>0.5038,0.0341,0.0178,0.5708</t>
-  </si>
-  <si>
-    <t>0.7937,0.1827,0.0190,0.0170</t>
-  </si>
-  <si>
-    <t>0.0533,0.9460,0.0266,0.0190</t>
-  </si>
-  <si>
-    <t>0.2276,0.7342,0.0073,0.0466</t>
-  </si>
-  <si>
-    <t>0.3693,0.7403,0.0251,0.0050</t>
-  </si>
-  <si>
-    <t>0.0180,0.9756,0.0089,0.0086</t>
-  </si>
-  <si>
-    <t>0.1010,0.9218,0.0374,0.0024</t>
-  </si>
-  <si>
-    <t>0.2366,0.8351,0.0135,0.0157</t>
-  </si>
-  <si>
-    <t>0.9021,0.1835,0.0043,0.0016</t>
-  </si>
-  <si>
-    <t>0.9705,0.0340,0.0028,0.0021</t>
-  </si>
-  <si>
-    <t>0.9776,0.0320,0.0017,0.0019</t>
-  </si>
-  <si>
-    <t>0.9698,0.0464,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9764,0.0315,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9778,0.0313,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9628,0.0626,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.9736,0.0353,0.0031,0.0016</t>
-  </si>
-  <si>
-    <t>0.0138,0.9877,0.0021,0.0020</t>
-  </si>
-  <si>
-    <t>0.3331,0.8455,0.0017,0.0021</t>
-  </si>
-  <si>
-    <t>0.1723,0.9285,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.1167,0.7849,0.2408,0.0061</t>
-  </si>
-  <si>
-    <t>0.9034,0.1673,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.7344,0.3754,0.0068,0.0045</t>
-  </si>
-  <si>
-    <t>0.9314,0.1017,0.0040,0.0024</t>
-  </si>
-  <si>
-    <t>0.6897,0.5008,0.0040,0.0022</t>
-  </si>
-  <si>
-    <t>0.0945,0.1228,0.8823,0.0159</t>
-  </si>
-  <si>
-    <t>0.8666,0.2483,0.0039,0.0016</t>
-  </si>
-  <si>
-    <t>0.0129,0.2439,0.9280,0.0345</t>
-  </si>
-  <si>
-    <t>0.0105,0.9402,0.3623,0.0119</t>
-  </si>
-  <si>
-    <t>0.0823,0.3229,0.7883,0.0134</t>
-  </si>
-  <si>
-    <t>0.0223,0.8384,0.2519,0.1469</t>
-  </si>
-  <si>
-    <t>0.0164,0.8152,0.6881,0.0104</t>
-  </si>
-  <si>
-    <t>0.0777,0.0710,0.8631,0.0497</t>
-  </si>
-  <si>
-    <t>0.0150,0.3924,0.9293,0.0090</t>
-  </si>
-  <si>
-    <t>0.0374,0.9284,0.1127,0.0149</t>
-  </si>
-  <si>
-    <t>0.1169,0.6853,0.3251,0.0302</t>
-  </si>
-  <si>
-    <t>0.0450,0.9366,0.0395,0.0242</t>
-  </si>
-  <si>
-    <t>0.0154,0.9692,0.0674,0.0016</t>
-  </si>
-  <si>
-    <t>0.0531,0.9330,0.0411,0.0130</t>
-  </si>
-  <si>
-    <t>0.0436,0.9563,0.0144,0.0116</t>
-  </si>
-  <si>
-    <t>0.0297,0.9568,0.0505,0.0072</t>
-  </si>
-  <si>
-    <t>0.0525,0.9162,0.0885,0.0131</t>
-  </si>
-  <si>
-    <t>0.0892,0.9582,0.0024,0.0017</t>
-  </si>
-  <si>
-    <t>0.4080,0.7808,0.0054,0.0022</t>
-  </si>
-  <si>
-    <t>0.7046,0.4925,0.0053,0.0019</t>
-  </si>
-  <si>
-    <t>0.9296,0.0708,0.0019,0.0062</t>
-  </si>
-  <si>
-    <t>0.4062,0.7600,0.0031,0.0036</t>
-  </si>
-  <si>
-    <t>0.0100,0.9831,0.0178,0.0047</t>
-  </si>
-  <si>
-    <t>0.2306,0.6174,0.0798,0.2468</t>
-  </si>
-  <si>
-    <t>0.1304,0.7214,0.0450,0.2553</t>
-  </si>
-  <si>
-    <t>0.6071,0.1183,0.2447,0.1092</t>
-  </si>
-  <si>
-    <t>0.0720,0.8142,0.0107,0.2124</t>
-  </si>
-  <si>
-    <t>0.1213,0.6447,0.1848,0.3560</t>
-  </si>
-  <si>
-    <t>0.0075,0.9249,0.0177,0.3522</t>
-  </si>
-  <si>
-    <t>0.0183,0.9166,0.2446,0.0533</t>
-  </si>
-  <si>
-    <t>0.0349,0.8596,0.1136,0.1625</t>
-  </si>
-  <si>
-    <t>0.0138,0.8532,0.0405,0.5398</t>
-  </si>
-  <si>
-    <t>0.9819,0.0158,0.0014,0.0029</t>
-  </si>
-  <si>
-    <t>0.9731,0.0460,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9702,0.0422,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.9771,0.0460,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9602,0.0469,0.0015,0.0033</t>
-  </si>
-  <si>
-    <t>0.9589,0.0722,0.0023,0.0013</t>
-  </si>
-  <si>
-    <t>0.9601,0.0541,0.0021,0.0026</t>
-  </si>
-  <si>
-    <t>0.9758,0.0248,0.0039,0.0030</t>
-  </si>
-  <si>
-    <t>0.3026,0.2914,0.5382,0.0317</t>
-  </si>
-  <si>
-    <t>0.0360,0.9389,0.1170,0.0046</t>
-  </si>
-  <si>
-    <t>0.7402,0.2483,0.0167,0.0442</t>
-  </si>
-  <si>
-    <t>0.0750,0.7931,0.3271,0.1138</t>
-  </si>
-  <si>
-    <t>0.0097,0.2808,0.7716,0.2219</t>
-  </si>
-  <si>
-    <t>0.0169,0.8138,0.4940,0.0639</t>
-  </si>
-  <si>
-    <t>0.0098,0.3901,0.5948,0.2878</t>
-  </si>
-  <si>
-    <t>0.0389,0.9308,0.0476,0.0695</t>
-  </si>
-  <si>
-    <t>0.0138,0.5252,0.6793,0.0910</t>
-  </si>
-  <si>
-    <t>0.0226,0.7748,0.2933,0.2207</t>
-  </si>
-  <si>
-    <t>0.0579,0.8856,0.1329,0.0499</t>
-  </si>
-  <si>
-    <t>0.0714,0.8844,0.1003,0.0597</t>
-  </si>
-  <si>
-    <t>0.3743,0.1586,0.1463,0.4177</t>
-  </si>
-  <si>
-    <t>0.1059,0.8666,0.0413,0.0503</t>
-  </si>
-  <si>
-    <t>0.9269,0.1092,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9759,0.0366,0.0025,0.0011</t>
-  </si>
-  <si>
-    <t>0.9696,0.0624,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9181,0.1224,0.0052,0.0020</t>
-  </si>
-  <si>
-    <t>0.9814,0.0163,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9542,0.0762,0.0025,0.0013</t>
-  </si>
-  <si>
-    <t>0.9600,0.0503,0.0019,0.0028</t>
-  </si>
-  <si>
-    <t>0.9482,0.0629,0.0024,0.0031</t>
-  </si>
-  <si>
-    <t>0.0225,0.9414,0.0505,0.1164</t>
-  </si>
-  <si>
-    <t>0.0632,0.5733,0.6255,0.0638</t>
-  </si>
-  <si>
-    <t>0.0132,0.9190,0.1584,0.1189</t>
-  </si>
-  <si>
-    <t>0.0319,0.9165,0.2165,0.0193</t>
-  </si>
-  <si>
-    <t>0.0509,0.0828,0.8588,0.0966</t>
-  </si>
-  <si>
-    <t>0.0258,0.6481,0.0198,0.8186</t>
-  </si>
-  <si>
-    <t>0.0528,0.8936,0.0691,0.1238</t>
-  </si>
-  <si>
-    <t>0.0142,0.8734,0.0360,0.5538</t>
-  </si>
-  <si>
-    <t>0.8157,0.0505,0.0134,0.1208</t>
-  </si>
-  <si>
-    <t>0.0029,0.7472,0.0011,0.9803</t>
-  </si>
-  <si>
-    <t>0.0146,0.0949,0.0021,0.9880</t>
-  </si>
-  <si>
-    <t>0.0030,0.0031,0.0013,0.9975</t>
-  </si>
-  <si>
-    <t>0.0020,0.0137,0.0024,0.9979</t>
-  </si>
-  <si>
-    <t>0.0510,0.8364,0.0121,0.4439</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.0528,0.9000,0.0071,0.0997</t>
+  </si>
+  <si>
+    <t>0.0147,0.0350,0.0024,0.9904</t>
+  </si>
+  <si>
+    <t>0.4174,0.1270,0.0070,0.4349</t>
+  </si>
+  <si>
+    <t>0.0193,0.2387,0.0047,0.9734</t>
+  </si>
+  <si>
+    <t>0.9877,0.0159,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9779,0.0256,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9830,0.0236,0.0031,0.0007</t>
+  </si>
+  <si>
+    <t>0.9829,0.0221,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.9816,0.0316,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9849,0.0153,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.9890,0.0080,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.9917,0.0082,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.0346,0.9518,0.0087,0.0357</t>
+  </si>
+  <si>
+    <t>0.1112,0.8478,0.1444,0.0197</t>
+  </si>
+  <si>
+    <t>0.0168,0.9697,0.0643,0.0027</t>
+  </si>
+  <si>
+    <t>0.0421,0.8948,0.1952,0.0145</t>
+  </si>
+  <si>
+    <t>0.1688,0.8052,0.1057,0.0306</t>
+  </si>
+  <si>
+    <t>0.0014,0.9979,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.9955,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.0165,0.9868,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.0019,0.9968,0.0007,0.0029</t>
+  </si>
+  <si>
+    <t>0.0020,0.9975,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.0298,0.9551,0.0251,0.0198</t>
+  </si>
+  <si>
+    <t>0.0395,0.9220,0.0442,0.0422</t>
+  </si>
+  <si>
+    <t>0.0317,0.1253,0.8006,0.2006</t>
+  </si>
+  <si>
+    <t>0.0795,0.7214,0.4109,0.0900</t>
+  </si>
+  <si>
+    <t>0.2131,0.0645,0.6897,0.1057</t>
+  </si>
+  <si>
+    <t>0.1048,0.4212,0.1645,0.5174</t>
+  </si>
+  <si>
+    <t>0.0127,0.0568,0.8498,0.2561</t>
+  </si>
+  <si>
+    <t>0.1202,0.9114,0.0081,0.0253</t>
+  </si>
+  <si>
+    <t>0.0959,0.8853,0.1085,0.0070</t>
+  </si>
+  <si>
+    <t>0.0949,0.3112,0.6297,0.1656</t>
+  </si>
+  <si>
+    <t>0.0152,0.9849,0.0129,0.0008</t>
+  </si>
+  <si>
+    <t>0.2330,0.8278,0.0296,0.0057</t>
+  </si>
+  <si>
+    <t>0.1544,0.8699,0.0331,0.0086</t>
+  </si>
+  <si>
+    <t>0.1951,0.8917,0.0057,0.0016</t>
+  </si>
+  <si>
+    <t>0.0093,0.9893,0.0200,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9747,0.0028,0.2026</t>
+  </si>
+  <si>
+    <t>0.0174,0.9474,0.0746,0.0862</t>
+  </si>
+  <si>
+    <t>0.0135,0.9414,0.2364,0.0238</t>
+  </si>
+  <si>
+    <t>0.0440,0.8117,0.1668,0.2622</t>
+  </si>
+  <si>
+    <t>0.0113,0.9727,0.0524,0.0260</t>
+  </si>
+  <si>
+    <t>0.0006,0.9989,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0293,0.8140,0.4813,0.0627</t>
+  </si>
+  <si>
+    <t>0.0183,0.9482,0.0022,0.2371</t>
+  </si>
+  <si>
+    <t>0.0007,0.9973,0.0009,0.0056</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.9026,0.0231,0.5200</t>
+  </si>
+  <si>
+    <t>0.0039,0.9728,0.0835,0.0560</t>
+  </si>
+  <si>
+    <t>0.0609,0.8447,0.1962,0.0621</t>
+  </si>
+  <si>
+    <t>0.0475,0.0773,0.8687,0.0830</t>
+  </si>
+  <si>
+    <t>0.0311,0.3827,0.5163,0.3631</t>
+  </si>
+  <si>
+    <t>0.0219,0.3843,0.5130,0.4172</t>
+  </si>
+  <si>
+    <t>0.8158,0.3491,0.0049,0.0015</t>
+  </si>
+  <si>
+    <t>0.9495,0.0548,0.0038,0.0046</t>
+  </si>
+  <si>
+    <t>0.9426,0.0925,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.0509,0.2505,0.8914,0.0166</t>
+  </si>
+  <si>
+    <t>0.9533,0.0618,0.0039,0.0026</t>
+  </si>
+  <si>
+    <t>0.9816,0.0244,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9783,0.0353,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.0039,0.9877,0.0176,0.0133</t>
+  </si>
+  <si>
+    <t>0.0115,0.8693,0.1218,0.3202</t>
+  </si>
+  <si>
+    <t>0.0374,0.7201,0.2568,0.3127</t>
+  </si>
+  <si>
+    <t>0.0030,0.9908,0.0191,0.0129</t>
+  </si>
+  <si>
+    <t>0.0158,0.7458,0.7586,0.0230</t>
+  </si>
+  <si>
+    <t>0.0018,0.9975,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.3561,0.6270,0.1102,0.0105</t>
+  </si>
+  <si>
+    <t>0.1177,0.8889,0.0617,0.0034</t>
+  </si>
+  <si>
+    <t>0.1057,0.4959,0.6311,0.0200</t>
+  </si>
+  <si>
+    <t>0.0013,0.9943,0.0337,0.0048</t>
+  </si>
+  <si>
+    <t>0.0005,0.9977,0.0039,0.0056</t>
+  </si>
+  <si>
+    <t>0.0014,0.9953,0.0099,0.0055</t>
+  </si>
+  <si>
+    <t>0.0005,0.9980,0.0016,0.0119</t>
+  </si>
+  <si>
+    <t>0.0075,0.0196,0.0049,0.9930</t>
+  </si>
+  <si>
+    <t>0.0040,0.1039,0.0012,0.9952</t>
+  </si>
+  <si>
+    <t>0.0022,0.0452,0.0008,0.9979</t>
+  </si>
+  <si>
+    <t>0.0359,0.0550,0.0049,0.9760</t>
+  </si>
+  <si>
+    <t>0.0157,0.0142,0.0015,0.9912</t>
+  </si>
+  <si>
+    <t>0.0075,0.0077,0.0009,0.9959</t>
+  </si>
+  <si>
+    <t>0.0011,0.9961,0.0027,0.0128</t>
+  </si>
+  <si>
+    <t>0.0047,0.9768,0.0683,0.0248</t>
+  </si>
+  <si>
+    <t>0.0017,0.9940,0.0213,0.0024</t>
+  </si>
+  <si>
+    <t>0.0091,0.9609,0.1115,0.0385</t>
+  </si>
+  <si>
+    <t>0.0016,0.9955,0.0063,0.0052</t>
+  </si>
+  <si>
+    <t>0.0023,0.9927,0.0094,0.0192</t>
+  </si>
+  <si>
+    <t>0.9867,0.0192,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9569,0.0938,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9617,0.0822,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9522,0.0737,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9727,0.0437,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9852,0.0187,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9803,0.0301,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9656,0.0550,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9902,0.0109,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9725,0.0440,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9903,0.0165,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9895,0.0105,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9706,0.0324,0.0009,0.0024</t>
+  </si>
+  <si>
+    <t>0.9863,0.0172,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9895,0.0103,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9916,0.0064,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.0556,0.4992,0.5590,0.1435</t>
+  </si>
+  <si>
+    <t>0.0354,0.9257,0.1328,0.0108</t>
+  </si>
+  <si>
+    <t>0.1769,0.7180,0.0858,0.1456</t>
+  </si>
+  <si>
+    <t>0.0477,0.8504,0.0789,0.2522</t>
+  </si>
+  <si>
+    <t>0.0043,0.9959,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.9971,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0203,0.9871,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.0414,0.9734,0.0050,0.0017</t>
+  </si>
+  <si>
+    <t>0.0044,0.9947,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.0024,0.9975,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.1482,0.9219,0.0038,0.0020</t>
+  </si>
+  <si>
+    <t>0.4724,0.4246,0.1351,0.0352</t>
+  </si>
+  <si>
+    <t>0.0281,0.8825,0.0432,0.3664</t>
+  </si>
+  <si>
+    <t>0.0120,0.9706,0.0058,0.0402</t>
+  </si>
+  <si>
+    <t>0.0299,0.9564,0.0155,0.0369</t>
+  </si>
+  <si>
+    <t>0.1018,0.7893,0.0245,0.2880</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.9967,0.0024,0.0032</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.0041,0.9959,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.0963,0.9427,0.0097,0.0013</t>
+  </si>
+  <si>
+    <t>0.0415,0.9757,0.0042,0.0011</t>
+  </si>
+  <si>
+    <t>0.9256,0.1506,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9584,0.0450,0.0017,0.0047</t>
+  </si>
+  <si>
+    <t>0.9835,0.0198,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9766,0.0276,0.0034,0.0027</t>
+  </si>
+  <si>
+    <t>0.9845,0.0156,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.9321,0.1194,0.0056,0.0009</t>
+  </si>
+  <si>
+    <t>0.9736,0.0334,0.0027,0.0020</t>
+  </si>
+  <si>
+    <t>0.9804,0.0204,0.0022,0.0029</t>
+  </si>
+  <si>
+    <t>0.0050,0.9762,0.1655,0.0047</t>
+  </si>
+  <si>
+    <t>0.0022,0.9924,0.0474,0.0035</t>
+  </si>
+  <si>
+    <t>0.0161,0.9582,0.0705,0.0334</t>
+  </si>
+  <si>
+    <t>0.0136,0.9578,0.1470,0.0162</t>
+  </si>
+  <si>
+    <t>0.0400,0.8408,0.0099,0.3242</t>
+  </si>
+  <si>
+    <t>0.0544,0.9377,0.0121,0.0312</t>
+  </si>
+  <si>
+    <t>0.2014,0.2342,0.6376,0.0464</t>
+  </si>
+  <si>
+    <t>0.1775,0.7482,0.0433,0.1124</t>
+  </si>
+  <si>
+    <t>0.0660,0.0355,0.0018,0.9637</t>
+  </si>
+  <si>
+    <t>0.0006,0.0065,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0018,0.1061,0.0013,0.9972</t>
+  </si>
+  <si>
+    <t>0.0086,0.0047,0.0010,0.9950</t>
+  </si>
+  <si>
+    <t>0.0012,0.9893,0.0061,0.0765</t>
+  </si>
+  <si>
+    <t>0.9423,0.0811,0.0017,0.0031</t>
+  </si>
+  <si>
+    <t>0.0276,0.9783,0.0012,0.0086</t>
+  </si>
+  <si>
+    <t>0.9516,0.0470,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.1150,0.9359,0.0020,0.0033</t>
+  </si>
+  <si>
+    <t>0.9688,0.0264,0.0028,0.0061</t>
+  </si>
+  <si>
+    <t>0.5675,0.0945,0.0226,0.2439</t>
+  </si>
+  <si>
+    <t>0.9357,0.0459,0.0041,0.0148</t>
+  </si>
+  <si>
+    <t>0.0123,0.2133,0.8738,0.1026</t>
+  </si>
+  <si>
+    <t>0.8536,0.0232,0.0174,0.1149</t>
+  </si>
+  <si>
+    <t>0.8838,0.0471,0.0097,0.0397</t>
+  </si>
+  <si>
+    <t>0.0815,0.9330,0.0101,0.0104</t>
+  </si>
+  <si>
+    <t>0.1953,0.8551,0.0062,0.0150</t>
+  </si>
+  <si>
+    <t>0.3425,0.7458,0.0214,0.0044</t>
+  </si>
+  <si>
+    <t>0.0146,0.9833,0.0099,0.0024</t>
+  </si>
+  <si>
+    <t>0.1488,0.8988,0.0215,0.0052</t>
+  </si>
+  <si>
+    <t>0.2857,0.7781,0.0096,0.0194</t>
+  </si>
+  <si>
+    <t>0.9803,0.0282,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.9780,0.0245,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9815,0.0292,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9829,0.0182,0.0040,0.0015</t>
+  </si>
+  <si>
+    <t>0.9851,0.0228,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9791,0.0314,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9717,0.0305,0.0039,0.0029</t>
+  </si>
+  <si>
+    <t>0.9856,0.0133,0.0015,0.0028</t>
+  </si>
+  <si>
+    <t>0.0115,0.9904,0.0032,0.0013</t>
+  </si>
+  <si>
+    <t>0.4734,0.7647,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.1757,0.9249,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.2137,0.7582,0.1405,0.0085</t>
+  </si>
+  <si>
+    <t>0.9251,0.1312,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.6203,0.5236,0.0042,0.0042</t>
+  </si>
+  <si>
+    <t>0.9173,0.1139,0.0071,0.0033</t>
+  </si>
+  <si>
+    <t>0.7378,0.3073,0.0044,0.0082</t>
+  </si>
+  <si>
+    <t>0.0610,0.2015,0.9104,0.0097</t>
+  </si>
+  <si>
+    <t>0.8325,0.2938,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.0241,0.1023,0.9188,0.0568</t>
+  </si>
+  <si>
+    <t>0.0241,0.8544,0.4241,0.0585</t>
+  </si>
+  <si>
+    <t>0.1146,0.2952,0.7840,0.0243</t>
+  </si>
+  <si>
+    <t>0.0395,0.8095,0.0610,0.3474</t>
+  </si>
+  <si>
+    <t>0.1059,0.4864,0.4854,0.1394</t>
+  </si>
+  <si>
+    <t>0.0385,0.1036,0.9161,0.0223</t>
+  </si>
+  <si>
+    <t>0.0169,0.3146,0.9126,0.0239</t>
+  </si>
+  <si>
+    <t>0.0297,0.9213,0.0477,0.0847</t>
+  </si>
+  <si>
+    <t>0.1114,0.6994,0.3316,0.0112</t>
+  </si>
+  <si>
+    <t>0.0337,0.9438,0.0789,0.0116</t>
+  </si>
+  <si>
+    <t>0.0135,0.9769,0.0474,0.0011</t>
+  </si>
+  <si>
+    <t>0.0689,0.8933,0.1240,0.0112</t>
+  </si>
+  <si>
+    <t>0.0305,0.9630,0.0055,0.0315</t>
+  </si>
+  <si>
+    <t>0.0347,0.9491,0.0338,0.0113</t>
+  </si>
+  <si>
+    <t>0.1430,0.6437,0.3217,0.0155</t>
+  </si>
+  <si>
+    <t>0.0683,0.9594,0.0041,0.0023</t>
+  </si>
+  <si>
+    <t>0.2403,0.8627,0.0069,0.0026</t>
+  </si>
+  <si>
+    <t>0.4528,0.6893,0.0110,0.0044</t>
+  </si>
+  <si>
+    <t>0.8134,0.3053,0.0037,0.0035</t>
+  </si>
+  <si>
+    <t>0.4301,0.7823,0.0033,0.0014</t>
+  </si>
+  <si>
+    <t>0.0840,0.8841,0.1174,0.0248</t>
+  </si>
+  <si>
+    <t>0.1499,0.3970,0.0304,0.5820</t>
+  </si>
+  <si>
+    <t>0.0437,0.8527,0.0157,0.2787</t>
+  </si>
+  <si>
+    <t>0.3407,0.4020,0.2962,0.1339</t>
+  </si>
+  <si>
+    <t>0.2893,0.3430,0.0478,0.3323</t>
+  </si>
+  <si>
+    <t>0.0446,0.7761,0.0920,0.4593</t>
+  </si>
+  <si>
+    <t>0.0050,0.8894,0.0104,0.6494</t>
+  </si>
+  <si>
+    <t>0.0092,0.9507,0.0404,0.1468</t>
+  </si>
+  <si>
+    <t>0.0629,0.7746,0.1253,0.2194</t>
+  </si>
+  <si>
+    <t>0.0228,0.9208,0.1090,0.1039</t>
+  </si>
+  <si>
+    <t>0.9773,0.0260,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9834,0.0228,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.8758,0.2274,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.9715,0.0523,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9846,0.0161,0.0011,0.0020</t>
+  </si>
+  <si>
+    <t>0.9763,0.0425,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9732,0.0294,0.0022,0.0027</t>
+  </si>
+  <si>
+    <t>0.9826,0.0232,0.0019,0.0014</t>
+  </si>
+  <si>
+    <t>0.1209,0.2907,0.7873,0.0156</t>
+  </si>
+  <si>
+    <t>0.0295,0.9518,0.0854,0.0037</t>
+  </si>
+  <si>
+    <t>0.3905,0.6115,0.0175,0.0538</t>
+  </si>
+  <si>
+    <t>0.0293,0.4263,0.8875,0.0144</t>
+  </si>
+  <si>
+    <t>0.0108,0.2190,0.9074,0.0622</t>
+  </si>
+  <si>
+    <t>0.0315,0.8126,0.4591,0.0615</t>
+  </si>
+  <si>
+    <t>0.0080,0.3547,0.8967,0.0407</t>
+  </si>
+  <si>
+    <t>0.0563,0.8547,0.2378,0.0598</t>
+  </si>
+  <si>
+    <t>0.0222,0.7438,0.2717,0.2552</t>
+  </si>
+  <si>
+    <t>0.0249,0.7684,0.4017,0.1238</t>
+  </si>
+  <si>
+    <t>0.1153,0.7591,0.2743,0.0380</t>
+  </si>
+  <si>
+    <t>0.0594,0.8681,0.0304,0.1312</t>
+  </si>
+  <si>
+    <t>0.1547,0.6502,0.1198,0.1872</t>
+  </si>
+  <si>
+    <t>0.0686,0.8871,0.0233,0.0414</t>
+  </si>
+  <si>
+    <t>0.9600,0.0567,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.9769,0.0274,0.0027,0.0015</t>
+  </si>
+  <si>
+    <t>0.9654,0.0556,0.0022,0.0015</t>
+  </si>
+  <si>
+    <t>0.9490,0.0806,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.9781,0.0192,0.0015,0.0034</t>
+  </si>
+  <si>
+    <t>0.9290,0.1474,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9521,0.0743,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9731,0.0331,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.0209,0.9584,0.0768,0.0112</t>
+  </si>
+  <si>
+    <t>0.0276,0.8394,0.4820,0.0251</t>
+  </si>
+  <si>
+    <t>0.0226,0.7068,0.3607,0.2484</t>
+  </si>
+  <si>
+    <t>0.0263,0.8866,0.3475,0.0094</t>
+  </si>
+  <si>
+    <t>0.0601,0.3299,0.7381,0.1219</t>
+  </si>
+  <si>
+    <t>0.0604,0.2493,0.0699,0.8566</t>
+  </si>
+  <si>
+    <t>0.0745,0.7680,0.3804,0.0410</t>
+  </si>
+  <si>
+    <t>0.0175,0.7207,0.0293,0.7478</t>
+  </si>
+  <si>
+    <t>0.4518,0.1542,0.0069,0.4438</t>
+  </si>
+  <si>
+    <t>0.0036,0.1803,0.0011,0.9935</t>
+  </si>
+  <si>
+    <t>0.0210,0.0213,0.0026,0.9872</t>
+  </si>
+  <si>
+    <t>0.0102,0.0061,0.0024,0.9926</t>
+  </si>
+  <si>
+    <t>0.0024,0.0063,0.0010,0.9982</t>
+  </si>
+  <si>
+    <t>0.2806,0.4939,0.0066,0.2961</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>262</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,10 +2340,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,10 +2494,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>262</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2581,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2634,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,10 +2662,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,10 +2690,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>262</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,10 +3446,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>262</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>262</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>262</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,10 +4426,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>262</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>262</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,10 +4552,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>262</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>262</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>262</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>262</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>262</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,10 +5056,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,10 +5070,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>262</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>262</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,10 +5140,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>262</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>262</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>262</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,10 +5350,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>262</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>262</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,10 +5462,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
